--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,15 +450,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4225</v>
+        <v>4060</v>
       </c>
       <c r="C2" t="n">
-        <v>15844</v>
+        <v>15225</v>
       </c>
       <c r="D2" t="n">
-        <v>0.76</v>
+        <v>-1.54</v>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>fallback (last known ±1.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4046</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15172</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>fallback (last known ±1.5%)</t>
         </is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4046</v>
+        <v>4205</v>
       </c>
       <c r="C3" t="n">
-        <v>15172</v>
+        <v>15769</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8</v>
+        <v>1.43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,15 +471,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4205</v>
+        <v>4421</v>
       </c>
       <c r="C3" t="n">
-        <v>15769</v>
+        <v>16579</v>
       </c>
       <c r="D3" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>fallback (last known ±1.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4439</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16646</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>fallback (last known ±1.5%)</t>
         </is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,18 +492,498 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4439</v>
+        <v>4381</v>
       </c>
       <c r="C4" t="n">
-        <v>16646</v>
+        <v>16429</v>
       </c>
       <c r="D4" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>fallback (last known ±1.5%)</t>
         </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4330</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16020603</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4209</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15571887</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4228</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15643782</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4191</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15508137</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4359</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16128800</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4381</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16208783</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4197</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15528248</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4032</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14918548</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4343</v>
+      </c>
+      <c r="C13" t="n">
+        <v>16070189</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4234</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15664769</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4010</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14837072</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4202</v>
+      </c>
+      <c r="C16" t="n">
+        <v>15548293</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>15263661</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4377</v>
+      </c>
+      <c r="C18" t="n">
+        <v>16196572</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4261</v>
+      </c>
+      <c r="C19" t="n">
+        <v>15766733</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4168</v>
+      </c>
+      <c r="C20" t="n">
+        <v>15421454</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4034</v>
+      </c>
+      <c r="C21" t="n">
+        <v>14925509</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4043</v>
+      </c>
+      <c r="C22" t="n">
+        <v>14960655</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4168</v>
+      </c>
+      <c r="C23" t="n">
+        <v>15421816</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4105</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15190349</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4029</v>
+      </c>
+      <c r="C25" t="n">
+        <v>14908960</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4093</v>
+      </c>
+      <c r="C26" t="n">
+        <v>15142314</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4082</v>
+      </c>
+      <c r="C27" t="n">
+        <v>15101861</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4360</v>
+      </c>
+      <c r="C28" t="n">
+        <v>16133261</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4289</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15869112</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4183</v>
+      </c>
+      <c r="C30" t="n">
+        <v>15478214</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4219</v>
+      </c>
+      <c r="C31" t="n">
+        <v>15610292</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4293</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15882660</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4104</v>
+      </c>
+      <c r="C33" t="n">
+        <v>15183836</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4252</v>
+      </c>
+      <c r="C34" t="n">
+        <v>15733594</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-2.21</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,6 +986,27 @@
         <v>-2.21</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4413</v>
+      </c>
+      <c r="C35" t="n">
+        <v>16549</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>fallback (last known ±1.5%)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4413</v>
+        <v>4500</v>
       </c>
       <c r="C35" t="n">
-        <v>16549</v>
+        <v>16875</v>
       </c>
       <c r="D35" t="n">
-        <v>1.18</v>
+        <v>0.05</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4500</v>
+        <v>4519</v>
       </c>
       <c r="C35" t="n">
-        <v>16875</v>
+        <v>16946</v>
       </c>
       <c r="D35" t="n">
-        <v>0.05</v>
+        <v>0.88</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4519</v>
+        <v>4564</v>
       </c>
       <c r="C35" t="n">
-        <v>16946</v>
+        <v>17115</v>
       </c>
       <c r="D35" t="n">
-        <v>0.88</v>
+        <v>-1.56</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4564</v>
+        <v>4483</v>
       </c>
       <c r="C35" t="n">
-        <v>17115</v>
+        <v>16811</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.56</v>
+        <v>1.26</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,626 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4483</v>
+        <v>4515</v>
       </c>
       <c r="C35" t="n">
-        <v>16811</v>
+        <v>16931</v>
       </c>
       <c r="D35" t="n">
-        <v>1.26</v>
+        <v>-0.42</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>fallback (last known ±1.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5068</v>
+      </c>
+      <c r="C36" t="n">
+        <v>19005</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>fallback (last known ±1.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-11.09</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
         </is>
       </c>
     </row>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1616,6 +1616,27 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4483</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4.483</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,6 +1637,27 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4483</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4.483</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,6 +1658,27 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4483</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4.483</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4506</v>
+        <v>4480</v>
       </c>
       <c r="C37" t="n">
-        <v>4.506</v>
+        <v>4.48</v>
       </c>
       <c r="D37" t="n">
-        <v>-11.09</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1052,628 +1052,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4506</v>
+        <v>4480</v>
       </c>
       <c r="C38" t="n">
-        <v>4.506</v>
+        <v>4.48</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C40" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C41" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C42" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C43" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C44" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C45" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C46" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C47" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C48" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C49" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C50" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C51" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C52" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C53" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C54" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C55" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C56" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C57" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C59" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C60" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C61" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>4506</v>
-      </c>
-      <c r="C64" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>4483</v>
-      </c>
-      <c r="C65" t="n">
-        <v>4.483</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>4483</v>
-      </c>
-      <c r="C66" t="n">
-        <v>4.483</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://tradingeconomics.com/commodity/palm-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>4483</v>
-      </c>
-      <c r="C67" t="n">
-        <v>4.483</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr">
         <is>
           <t>https://tradingeconomics.com/commodity/palm-oil</t>
         </is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -453,7 +453,7 @@
         <v>4060</v>
       </c>
       <c r="C2" t="n">
-        <v>15225</v>
+        <v>73080</v>
       </c>
       <c r="D2" t="n">
         <v>-1.54</v>
@@ -474,7 +474,7 @@
         <v>4421</v>
       </c>
       <c r="C3" t="n">
-        <v>16579</v>
+        <v>79578</v>
       </c>
       <c r="D3" t="n">
         <v>1.77</v>
@@ -495,7 +495,7 @@
         <v>4381</v>
       </c>
       <c r="C4" t="n">
-        <v>16429</v>
+        <v>78858</v>
       </c>
       <c r="D4" t="n">
         <v>0.8</v>
@@ -516,7 +516,7 @@
         <v>4330</v>
       </c>
       <c r="C5" t="n">
-        <v>16020603</v>
+        <v>77940</v>
       </c>
       <c r="D5" t="n">
         <v>-2.1</v>
@@ -532,7 +532,7 @@
         <v>4209</v>
       </c>
       <c r="C6" t="n">
-        <v>15571887</v>
+        <v>75762</v>
       </c>
       <c r="D6" t="n">
         <v>-1.81</v>
@@ -548,7 +548,7 @@
         <v>4228</v>
       </c>
       <c r="C7" t="n">
-        <v>15643782</v>
+        <v>76104</v>
       </c>
       <c r="D7" t="n">
         <v>-1.52</v>
@@ -564,7 +564,7 @@
         <v>4191</v>
       </c>
       <c r="C8" t="n">
-        <v>15508137</v>
+        <v>75438</v>
       </c>
       <c r="D8" t="n">
         <v>-1.34</v>
@@ -580,7 +580,7 @@
         <v>4359</v>
       </c>
       <c r="C9" t="n">
-        <v>16128800</v>
+        <v>78462</v>
       </c>
       <c r="D9" t="n">
         <v>0.19</v>
@@ -596,7 +596,7 @@
         <v>4381</v>
       </c>
       <c r="C10" t="n">
-        <v>16208783</v>
+        <v>78858</v>
       </c>
       <c r="D10" t="n">
         <v>1.63</v>
@@ -612,7 +612,7 @@
         <v>4197</v>
       </c>
       <c r="C11" t="n">
-        <v>15528248</v>
+        <v>75546</v>
       </c>
       <c r="D11" t="n">
         <v>1.43</v>
@@ -628,7 +628,7 @@
         <v>4032</v>
       </c>
       <c r="C12" t="n">
-        <v>14918548</v>
+        <v>72576</v>
       </c>
       <c r="D12" t="n">
         <v>-2.34</v>
@@ -644,7 +644,7 @@
         <v>4343</v>
       </c>
       <c r="C13" t="n">
-        <v>16070189</v>
+        <v>78174</v>
       </c>
       <c r="D13" t="n">
         <v>1.07</v>
@@ -660,7 +660,7 @@
         <v>4234</v>
       </c>
       <c r="C14" t="n">
-        <v>15664769</v>
+        <v>76212</v>
       </c>
       <c r="D14" t="n">
         <v>-2.24</v>
@@ -676,7 +676,7 @@
         <v>4010</v>
       </c>
       <c r="C15" t="n">
-        <v>14837072</v>
+        <v>72180</v>
       </c>
       <c r="D15" t="n">
         <v>-1.05</v>
@@ -692,7 +692,7 @@
         <v>4202</v>
       </c>
       <c r="C16" t="n">
-        <v>15548293</v>
+        <v>75636</v>
       </c>
       <c r="D16" t="n">
         <v>-1.97</v>
@@ -708,7 +708,7 @@
         <v>4125</v>
       </c>
       <c r="C17" t="n">
-        <v>15263661</v>
+        <v>74250</v>
       </c>
       <c r="D17" t="n">
         <v>1.67</v>
@@ -724,7 +724,7 @@
         <v>4377</v>
       </c>
       <c r="C18" t="n">
-        <v>16196572</v>
+        <v>78786</v>
       </c>
       <c r="D18" t="n">
         <v>-0.08</v>
@@ -740,7 +740,7 @@
         <v>4261</v>
       </c>
       <c r="C19" t="n">
-        <v>15766733</v>
+        <v>76698</v>
       </c>
       <c r="D19" t="n">
         <v>0.32</v>
@@ -756,7 +756,7 @@
         <v>4168</v>
       </c>
       <c r="C20" t="n">
-        <v>15421454</v>
+        <v>75024</v>
       </c>
       <c r="D20" t="n">
         <v>-0.11</v>
@@ -772,7 +772,7 @@
         <v>4034</v>
       </c>
       <c r="C21" t="n">
-        <v>14925509</v>
+        <v>72612</v>
       </c>
       <c r="D21" t="n">
         <v>-2.21</v>
@@ -788,7 +788,7 @@
         <v>4043</v>
       </c>
       <c r="C22" t="n">
-        <v>14960655</v>
+        <v>72774</v>
       </c>
       <c r="D22" t="n">
         <v>1.47</v>
@@ -804,7 +804,7 @@
         <v>4168</v>
       </c>
       <c r="C23" t="n">
-        <v>15421816</v>
+        <v>75024</v>
       </c>
       <c r="D23" t="n">
         <v>-0.41</v>
@@ -820,7 +820,7 @@
         <v>4105</v>
       </c>
       <c r="C24" t="n">
-        <v>15190349</v>
+        <v>73890</v>
       </c>
       <c r="D24" t="n">
         <v>-0.83</v>
@@ -836,7 +836,7 @@
         <v>4029</v>
       </c>
       <c r="C25" t="n">
-        <v>14908960</v>
+        <v>72522</v>
       </c>
       <c r="D25" t="n">
         <v>-0.84</v>
@@ -852,7 +852,7 @@
         <v>4093</v>
       </c>
       <c r="C26" t="n">
-        <v>15142314</v>
+        <v>73674</v>
       </c>
       <c r="D26" t="n">
         <v>-2.24</v>
@@ -868,7 +868,7 @@
         <v>4082</v>
       </c>
       <c r="C27" t="n">
-        <v>15101861</v>
+        <v>73476</v>
       </c>
       <c r="D27" t="n">
         <v>-1.55</v>
@@ -884,7 +884,7 @@
         <v>4360</v>
       </c>
       <c r="C28" t="n">
-        <v>16133261</v>
+        <v>78480</v>
       </c>
       <c r="D28" t="n">
         <v>-0.01</v>
@@ -900,7 +900,7 @@
         <v>4289</v>
       </c>
       <c r="C29" t="n">
-        <v>15869112</v>
+        <v>77202</v>
       </c>
       <c r="D29" t="n">
         <v>1.19</v>
@@ -916,7 +916,7 @@
         <v>4183</v>
       </c>
       <c r="C30" t="n">
-        <v>15478214</v>
+        <v>75294</v>
       </c>
       <c r="D30" t="n">
         <v>-2.39</v>
@@ -932,7 +932,7 @@
         <v>4219</v>
       </c>
       <c r="C31" t="n">
-        <v>15610292</v>
+        <v>75942</v>
       </c>
       <c r="D31" t="n">
         <v>0.22</v>
@@ -948,7 +948,7 @@
         <v>4293</v>
       </c>
       <c r="C32" t="n">
-        <v>15882660</v>
+        <v>77274</v>
       </c>
       <c r="D32" t="n">
         <v>-1.06</v>
@@ -964,7 +964,7 @@
         <v>4104</v>
       </c>
       <c r="C33" t="n">
-        <v>15183836</v>
+        <v>73872</v>
       </c>
       <c r="D33" t="n">
         <v>1.36</v>
@@ -980,7 +980,7 @@
         <v>4252</v>
       </c>
       <c r="C34" t="n">
-        <v>15733594</v>
+        <v>76536</v>
       </c>
       <c r="D34" t="n">
         <v>-2.21</v>
@@ -996,7 +996,7 @@
         <v>4515</v>
       </c>
       <c r="C35" t="n">
-        <v>16931</v>
+        <v>81270</v>
       </c>
       <c r="D35" t="n">
         <v>-0.42</v>
@@ -1017,7 +1017,7 @@
         <v>5068</v>
       </c>
       <c r="C36" t="n">
-        <v>19005</v>
+        <v>91224</v>
       </c>
       <c r="D36" t="n">
         <v>-1.91</v>
@@ -1038,7 +1038,7 @@
         <v>4480</v>
       </c>
       <c r="C37" t="n">
-        <v>4.48</v>
+        <v>80640</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>4480</v>
       </c>
       <c r="C38" t="n">
-        <v>4.48</v>
+        <v>80640</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,6 +1070,27 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4480</v>
+      </c>
+      <c r="C39" t="n">
+        <v>80640</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,48 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4550</v>
+      </c>
+      <c r="C40" t="n">
+        <v>81900</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4550</v>
+      </c>
+      <c r="C41" t="n">
+        <v>81900</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,15 +1119,36 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4550</v>
+        <v>4547</v>
       </c>
       <c r="C41" t="n">
-        <v>81900</v>
+        <v>81846</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E41" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4609</v>
+      </c>
+      <c r="C42" t="n">
+        <v>82962</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>https://tradingeconomics.com/commodity/palm-oil</t>
         </is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,6 +1154,27 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4609</v>
+      </c>
+      <c r="C43" t="n">
+        <v>82962</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1161,15 +1161,36 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4609</v>
+        <v>4594</v>
       </c>
       <c r="C43" t="n">
-        <v>82962</v>
+        <v>82692</v>
       </c>
       <c r="D43" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4594</v>
+      </c>
+      <c r="C44" t="n">
+        <v>82692</v>
+      </c>
+      <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>https://tradingeconomics.com/commodity/palm-oil</t>
         </is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1182,15 +1182,78 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4594</v>
+        <v>4513</v>
       </c>
       <c r="C44" t="n">
-        <v>82692</v>
+        <v>81234</v>
       </c>
       <c r="D44" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4513</v>
+      </c>
+      <c r="C45" t="n">
+        <v>81234</v>
+      </c>
+      <c r="D45" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4513</v>
+      </c>
+      <c r="C46" t="n">
+        <v>81234</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4513</v>
+      </c>
+      <c r="C47" t="n">
+        <v>81234</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://tradingeconomics.com/commodity/palm-oil</t>
         </is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,15 +1245,57 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4513</v>
+        <v>4533</v>
       </c>
       <c r="C47" t="n">
-        <v>81234</v>
+        <v>81594</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="E47" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4573</v>
+      </c>
+      <c r="C48" t="n">
+        <v>82314</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4569</v>
+      </c>
+      <c r="C49" t="n">
+        <v>82242</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>https://tradingeconomics.com/commodity/palm-oil</t>
         </is>

--- a/data/harga_cpo.xlsx
+++ b/data/harga_cpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,6 +1301,174 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4574</v>
+      </c>
+      <c r="C50" t="n">
+        <v>82332</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4565</v>
+      </c>
+      <c r="C51" t="n">
+        <v>82170</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4565</v>
+      </c>
+      <c r="C52" t="n">
+        <v>82170</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4565</v>
+      </c>
+      <c r="C53" t="n">
+        <v>82170</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4643</v>
+      </c>
+      <c r="C54" t="n">
+        <v>83574</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4610</v>
+      </c>
+      <c r="C55" t="n">
+        <v>82980</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4622</v>
+      </c>
+      <c r="C56" t="n">
+        <v>83196</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4622</v>
+      </c>
+      <c r="C57" t="n">
+        <v>83196</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/commodity/palm-oil</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
